--- a/backend/limit.xlsx
+++ b/backend/limit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="11_5054ACC319476E71AF1307377EA64A8F4C9F978C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5D15C07-D0AB-4F93-BC87-C33D95432CD4}"/>
+  <xr:revisionPtr revIDLastSave="504" documentId="11_5054ACC319476E71AF1307377EA64A8F4C9F978C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A13FF68-1B95-42BC-8017-5BC7313D12BB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,10 +777,10 @@
     <t>นาง รัชฎาภรณ์ มังคละเกษม 14/11/2025 14/11/2026</t>
   </si>
   <si>
-    <t>นางสาว นิอร หาญวัฒนาศิริ 16/07/2026 12/10/2026</t>
-  </si>
-  <si>
     <t>นางสาว นิอร หาญวัฒนาศิริ 28/09/2026 25/12/2026</t>
+  </si>
+  <si>
+    <t>นางสาว นิอร หาญวัฒนาศิริ 12/10/2026 08/01/2027</t>
   </si>
   <si>
     <t>ห้างหุ้นส่วนจำกัด ที.พี.บี การโยธา 04/07/2024 19/03/2027</t>
@@ -16940,7 +16940,7 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="15">
-        <v>863124915118</v>
+        <v>863128513505</v>
       </c>
       <c r="B138" s="15" t="s">
         <v>238</v>
@@ -16956,7 +16956,7 @@
         <v>นางสาว นิอร หาญวัฒนาศิริ</v>
       </c>
       <c r="F138" s="16">
-        <v>425600</v>
+        <v>700000</v>
       </c>
       <c r="G138" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -16966,7 +16966,7 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="15">
-        <v>863124915134</v>
+        <v>863128513653</v>
       </c>
       <c r="B139" s="15" t="s">
         <v>238</v>
@@ -16982,7 +16982,7 @@
         <v>นางสาว นิอร หาญวัฒนาศิริ</v>
       </c>
       <c r="F139" s="16">
-        <v>646000</v>
+        <v>500000</v>
       </c>
       <c r="G139" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -16992,7 +16992,7 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="15">
-        <v>863124915167</v>
+        <v>863128513885</v>
       </c>
       <c r="B140" s="15" t="s">
         <v>238</v>
@@ -17008,7 +17008,7 @@
         <v>นางสาว นิอร หาญวัฒนาศิริ</v>
       </c>
       <c r="F140" s="16">
-        <v>28400</v>
+        <v>500000</v>
       </c>
       <c r="G140" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -17018,7 +17018,7 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="15">
-        <v>863128513505</v>
+        <v>863129062593</v>
       </c>
       <c r="B141" s="15" t="s">
         <v>239</v>
@@ -17034,17 +17034,17 @@
         <v>นางสาว นิอร หาญวัฒนาศิริ</v>
       </c>
       <c r="F141" s="16">
-        <v>700000</v>
+        <v>425600</v>
       </c>
       <c r="G141" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="15">
-        <v>863128513653</v>
+        <v>863129062676</v>
       </c>
       <c r="B142" s="15" t="s">
         <v>239</v>
@@ -17060,17 +17060,17 @@
         <v>นางสาว นิอร หาญวัฒนาศิริ</v>
       </c>
       <c r="F142" s="16">
-        <v>500000</v>
+        <v>646000</v>
       </c>
       <c r="G142" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="2"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="15">
-        <v>863128513885</v>
+        <v>863129062817</v>
       </c>
       <c r="B143" s="15" t="s">
         <v>239</v>
@@ -17086,11 +17086,11 @@
         <v>นางสาว นิอร หาญวัฒนาศิริ</v>
       </c>
       <c r="F143" s="16">
-        <v>500000</v>
+        <v>28400</v>
       </c>
       <c r="G143" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H143" s="2"/>
     </row>
@@ -19630,7 +19630,7 @@
         <v>นาย อาทิตย์ มีโส</v>
       </c>
       <c r="F236" s="16">
-        <v>64869.61</v>
+        <v>60869.61</v>
       </c>
       <c r="G236" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -23158,7 +23158,7 @@
         <v>จาฏุพัจน์ จูมเอ้ย</v>
       </c>
       <c r="F362" s="16">
-        <v>15992</v>
+        <v>15658</v>
       </c>
       <c r="G362" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -26138,7 +26138,7 @@
         <v>นางสาว สุพรรษา ปาดี</v>
       </c>
       <c r="F472" s="16">
-        <v>71509.11</v>
+        <v>69400.210000000006</v>
       </c>
       <c r="G472" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -26616,7 +26616,7 @@
         <v>นางสาว มัลลิกา โชติสีนิล</v>
       </c>
       <c r="F490" s="16">
-        <v>146516.82999999999</v>
+        <v>143609.67000000001</v>
       </c>
       <c r="G490" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -29024,7 +29024,7 @@
         <v>นาง จาริณี ชัยสุขขจี</v>
       </c>
       <c r="F576" s="16">
-        <v>868952.4</v>
+        <v>867777.35</v>
       </c>
       <c r="G576" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -29472,7 +29472,7 @@
         <v>นาย รณยุทธ นามเสนา</v>
       </c>
       <c r="F592" s="16">
-        <v>224540.21</v>
+        <v>223900.21</v>
       </c>
       <c r="G592" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -31068,7 +31068,7 @@
         <v>นาย บุญส่ง ทาป้อง</v>
       </c>
       <c r="F649" s="16">
-        <v>2792.07</v>
+        <v>1803.6</v>
       </c>
       <c r="G649" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -66580,7 +66580,7 @@
         <v>ประจวบ จันทร์คำ</v>
       </c>
       <c r="F1939" s="16">
-        <v>7768</v>
+        <v>7212</v>
       </c>
       <c r="G1939" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -69770,7 +69770,7 @@
         <v>สมปฤดี ใสยิ่ง</v>
       </c>
       <c r="F2053" s="16">
-        <v>6994</v>
+        <v>6827</v>
       </c>
       <c r="G2053" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -69826,7 +69826,7 @@
         <v>อาทิตย์ธวัช จันโสดา</v>
       </c>
       <c r="F2055" s="16">
-        <v>7534.61</v>
+        <v>7495</v>
       </c>
       <c r="G2055" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -69938,7 +69938,7 @@
         <v>หนึ่งฤทัย จันโสดา</v>
       </c>
       <c r="F2059" s="16">
-        <v>15324</v>
+        <v>14990</v>
       </c>
       <c r="G2059" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -70050,7 +70050,7 @@
         <v>ฝ้าย สอนงอก</v>
       </c>
       <c r="F2063" s="16">
-        <v>15324</v>
+        <v>14990</v>
       </c>
       <c r="G2063" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -72986,7 +72986,7 @@
         <v>โสภาวดี อุ่นใจ</v>
       </c>
       <c r="F2168" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2168" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73238,7 +73238,7 @@
         <v>วณิชาดา คำเครื่อง</v>
       </c>
       <c r="F2177" s="16">
-        <v>5830</v>
+        <v>4996</v>
       </c>
       <c r="G2177" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73350,7 +73350,7 @@
         <v>วรรณวิภา คำปล้อง</v>
       </c>
       <c r="F2181" s="16">
-        <v>4664</v>
+        <v>4080</v>
       </c>
       <c r="G2181" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73406,7 +73406,7 @@
         <v>สุดารัตน์ ล้อสินคำ</v>
       </c>
       <c r="F2183" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2183" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73490,7 +73490,7 @@
         <v>ภรณ์สุดา ธิติตระกูล</v>
       </c>
       <c r="F2186" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2186" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73518,7 +73518,7 @@
         <v>พรพิมล กำมาแสน</v>
       </c>
       <c r="F2187" s="16">
-        <v>4664</v>
+        <v>4080</v>
       </c>
       <c r="G2187" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73602,7 +73602,7 @@
         <v>ต๋อย มาง้าว</v>
       </c>
       <c r="F2190" s="16">
-        <v>3332</v>
+        <v>2915</v>
       </c>
       <c r="G2190" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73686,7 +73686,7 @@
         <v>วุฒินันท์ คำบ้อน</v>
       </c>
       <c r="F2193" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2193" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73798,7 +73798,7 @@
         <v>นริศรา วงษ์ลา</v>
       </c>
       <c r="F2197" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2197" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73826,7 +73826,7 @@
         <v>วาสนา คำสาเลา</v>
       </c>
       <c r="F2198" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2198" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73910,7 +73910,7 @@
         <v>ภรณ์ทิยา จงแจ่มฟ้า</v>
       </c>
       <c r="F2201" s="16">
-        <v>4664</v>
+        <v>4080</v>
       </c>
       <c r="G2201" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>

--- a/backend/limit.xlsx
+++ b/backend/limit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="504" documentId="11_5054ACC319476E71AF1307377EA64A8F4C9F978C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A13FF68-1B95-42BC-8017-5BC7313D12BB}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="11_5054ACC319476E71AF1307377EA64A8F4C9F978C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42B53FFA-25C2-4C5F-99A5-D81C7B982FAA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18174,7 +18174,7 @@
         <v>นาง เรณู ศรีเมืองสุข</v>
       </c>
       <c r="F182" s="16">
-        <v>94422.49</v>
+        <v>94183.67</v>
       </c>
       <c r="G182" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -25228,7 +25228,7 @@
         <v>นาง เรณู พันธ์ทอง</v>
       </c>
       <c r="F437" s="16">
-        <v>109998.34</v>
+        <v>109968.34</v>
       </c>
       <c r="G437" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -29472,7 +29472,7 @@
         <v>นาย รณยุทธ นามเสนา</v>
       </c>
       <c r="F592" s="16">
-        <v>223900.21</v>
+        <v>222702.21</v>
       </c>
       <c r="G592" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -30340,7 +30340,7 @@
         <v>นางสาว เสาวภา จันโสดา</v>
       </c>
       <c r="F623" s="16">
-        <v>209129.92</v>
+        <v>209079.92</v>
       </c>
       <c r="G623" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -34344,7 +34344,7 @@
         <v>นาง มะลิ อยู่สวัสดิ์</v>
       </c>
       <c r="F766" s="16">
-        <v>39975.97</v>
+        <v>39475.97</v>
       </c>
       <c r="G766" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -34890,7 +34890,7 @@
         <v>กัลยาณวรรณ รัตนวีรพงษ์</v>
       </c>
       <c r="F787" s="16">
-        <v>9666</v>
+        <v>9499</v>
       </c>
       <c r="G787" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -57342,7 +57342,7 @@
         <v>นางสาว สุทธิภาภรณ์ ปานธูป</v>
       </c>
       <c r="F1604" s="16">
-        <v>107984.27</v>
+        <v>107784.27</v>
       </c>
       <c r="G1604" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -64236,7 +64236,7 @@
         <v>นางสาว สมร โกวิทชัย</v>
       </c>
       <c r="F1855" s="16">
-        <v>510011.51</v>
+        <v>509250.36</v>
       </c>
       <c r="G1855" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -69910,7 +69910,7 @@
         <v>สยาม หอมอ่อน</v>
       </c>
       <c r="F2058" s="16">
-        <v>15324</v>
+        <v>14990</v>
       </c>
       <c r="G2058" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -69966,7 +69966,7 @@
         <v>หทัยรัตน์ ทนันไชย</v>
       </c>
       <c r="F2060" s="16">
-        <v>7161</v>
+        <v>6994</v>
       </c>
       <c r="G2060" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -70582,7 +70582,7 @@
         <v>ธนพัต ขันใจ</v>
       </c>
       <c r="F2082" s="16">
-        <v>7829</v>
+        <v>7662</v>
       </c>
       <c r="G2082" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -70886,7 +70886,7 @@
         <v>สมุทร แซ่เตียว</v>
       </c>
       <c r="F2093" s="16">
-        <v>7495</v>
+        <v>7328</v>
       </c>
       <c r="G2093" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73378,7 +73378,7 @@
         <v>วรินดา เท็นผม</v>
       </c>
       <c r="F2182" s="16">
-        <v>5830</v>
+        <v>4996</v>
       </c>
       <c r="G2182" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73938,7 +73938,7 @@
         <v>จิรวัฒน์ อินสุ</v>
       </c>
       <c r="F2202" s="16">
-        <v>3332</v>
+        <v>2915</v>
       </c>
       <c r="G2202" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73966,7 +73966,7 @@
         <v>ชัยรัตน์ ตันเต็ม</v>
       </c>
       <c r="F2203" s="16">
-        <v>3332</v>
+        <v>2915</v>
       </c>
       <c r="G2203" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -73994,7 +73994,7 @@
         <v>สายสุนีย์ เจียมรัมย์</v>
       </c>
       <c r="F2204" s="16">
-        <v>3332</v>
+        <v>2915</v>
       </c>
       <c r="G2204" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -74050,7 +74050,7 @@
         <v>รุ้งทอง ยิ้มนิยม</v>
       </c>
       <c r="F2206" s="16">
-        <v>6664</v>
+        <v>5830</v>
       </c>
       <c r="G2206" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -74078,7 +74078,7 @@
         <v>วัชราภรณ์ คำอิ่น</v>
       </c>
       <c r="F2207" s="16">
-        <v>6664</v>
+        <v>6643.18</v>
       </c>
       <c r="G2207" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -74106,7 +74106,7 @@
         <v>รภัสสา ทุมลา</v>
       </c>
       <c r="F2208" s="16">
-        <v>4664</v>
+        <v>4080</v>
       </c>
       <c r="G2208" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -74134,7 +74134,7 @@
         <v>จิราภา สุวิลัย</v>
       </c>
       <c r="F2209" s="16">
-        <v>3332</v>
+        <v>3151.2</v>
       </c>
       <c r="G2209" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -74162,7 +74162,7 @@
         <v>ติ๋ม ไพสีทา</v>
       </c>
       <c r="F2210" s="16">
-        <v>3332</v>
+        <v>2915</v>
       </c>
       <c r="G2210" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -74190,7 +74190,7 @@
         <v>สำเนียง อ่องดา</v>
       </c>
       <c r="F2211" s="16">
-        <v>3332</v>
+        <v>2915</v>
       </c>
       <c r="G2211" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -77270,7 +77270,7 @@
         <v>เกศรา หมอนตอง</v>
       </c>
       <c r="F2321" s="16">
-        <v>44162</v>
+        <v>43584.4</v>
       </c>
       <c r="G2321" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
@@ -77298,7 +77298,7 @@
         <v>สุพีรณัฐ ตั้วสกุล</v>
       </c>
       <c r="F2322" s="16">
-        <v>71248.5</v>
+        <v>69998</v>
       </c>
       <c r="G2322" s="13">
         <f>(RIGHT(Table1[[#This Row],[NAME]],4))-2025</f>
